--- a/docs/DMA Usage.xlsx
+++ b/docs/DMA Usage.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -589,13 +589,119 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.82"/>
@@ -800,7 +906,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -1097,7 +1203,7 @@
       <c r="C21" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="9" t="s">
         <v>88</v>
       </c>
       <c r="E21" s="8" t="s">
@@ -1112,7 +1218,7 @@
       <c r="H21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I21" s="9" t="s">
         <v>90</v>
       </c>
     </row>

--- a/docs/DMA Usage.xlsx
+++ b/docs/DMA Usage.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -589,119 +589,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
-  <a:themeElements>
-    <a:clrScheme name="LibreOffice">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="ffffff"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="000000"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="ffffff"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="18a303"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="0369a3"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="a33e03"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8e03a3"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="c99c00"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="c9211e"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000ee"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="551a8b"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.82"/>
@@ -906,17 +800,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="8" t="s">

--- a/docs/DMA Usage.xlsx
+++ b/docs/DMA Usage.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="107">
   <si>
     <t xml:space="preserve">STM32F437VG</t>
   </si>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">UART4_RX</t>
   </si>
   <si>
-    <t xml:space="preserve">USART3_TX</t>
+    <t xml:space="preserve">*USART3_TX</t>
   </si>
   <si>
     <t xml:space="preserve">UART4_TX</t>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t xml:space="preserve">UART5_TX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* conflict with SPI2_RX</t>
   </si>
   <si>
     <t xml:space="preserve">Channel 5</t>
@@ -216,6 +219,9 @@
   </si>
   <si>
     <t xml:space="preserve">I2C2_RX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USART3_TX</t>
   </si>
   <si>
     <t xml:space="preserve">DAC1</t>
@@ -420,7 +426,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -431,6 +437,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF81D41A"/>
         <bgColor rgb="FF969696"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFAA95"/>
+        <bgColor rgb="FFFFCC99"/>
       </patternFill>
     </fill>
   </fills>
@@ -468,7 +480,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -511,6 +523,14 @@
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -565,7 +585,7 @@
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFAA95"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
       <rgbColor rgb="FF3366FF"/>
@@ -589,20 +609,125 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
-  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L28"/>
+  <sheetFormatPr defaultColWidth="10.8203125" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11.77"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="11.8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="10.45"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="1" width="10.82"/>
@@ -784,7 +909,7 @@
       <c r="D9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="10" t="s">
         <v>32</v>
       </c>
       <c r="F9" s="10" t="s">
@@ -800,7 +925,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
         <v>37</v>
       </c>
@@ -813,7 +938,7 @@
       <c r="D10" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F10" s="8" t="s">
@@ -828,60 +953,64 @@
       <c r="I10" s="8" t="s">
         <v>45</v>
       </c>
+      <c r="K10" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H11" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>47</v>
-      </c>
       <c r="I11" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="F12" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>13</v>
@@ -889,36 +1018,36 @@
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -931,7 +1060,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -976,25 +1105,25 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>68</v>
-      </c>
       <c r="G17" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="I17" s="10" t="s">
         <v>13</v>
@@ -1008,25 +1137,25 @@
         <v>13</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>71</v>
-      </c>
       <c r="G18" s="8" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1034,25 +1163,25 @@
         <v>21</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>13</v>
@@ -1063,22 +1192,22 @@
         <v>29</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H20" s="8" t="s">
         <v>13</v>
@@ -1092,83 +1221,83 @@
         <v>37</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>13</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>13</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I23" s="10" t="s">
         <v>13</v>
@@ -1176,31 +1305,31 @@
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>13</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1226,12 +1355,12 @@
       <c r="I26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>104</v>
+      <c r="A27" s="13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11"/>
+      <c r="A28" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
